--- a/output/2026-10-05_23_Croazia_Međimurska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-05_23_Croazia_Međimurska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distribuzione/ingrosso utensili manuali e accessori professionali, brand proprio MAX, oltre 5000 articoli a catalogo, oltre 1000-1500 clienti attivi (rivenditori/retail/ferramenta). Distributore puro B2B.</t>
+          <t>Distribuzione/ingrosso utensili manuali e accessori professionali, brand proprio MAX, oltre 5000 articoli a catalogo, oltre 1000-1500 clienti attivi (rivenditori/retail/ferramenta). Distributore puro B2B. [DUPLICATO — vedi anche: 2026-09-16_01_Croazia_Brodsko-posavska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Distributore autorizzato utensili elettrici, abrasivi, punte, attrezzature saldatura/riscaldamento, DPI; brand distribuiti Bosch, Tyrolit, Norton, 3M, Lacuna. Oltre 30 anni di attività, assistenza tecnica e ricambi Bosch.</t>
+          <t>Distributore autorizzato utensili elettrici, abrasivi, punte, attrezzature saldatura/riscaldamento, DPI; brand distribuiti Bosch, Tyrolit, Norton, 3M, Lacuna. Oltre 30 anni di attività, assistenza tecnica e ricambi Bosch. [DUPLICATO — vedi anche: 2026-09-08_06_Croazia_Krapinsko-zagorska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/output/2026-10-05_23_Croazia_Međimurska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-05_23_Croazia_Međimurska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
